--- a/inspection_forms/030_inspection_checklist_submission_acknowledgement_form--inspection_forms.xlsx
+++ b/inspection_forms/030_inspection_checklist_submission_acknowledgement_form--inspection_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="43" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Other (specify)</t>
+          <t>Submitter Comments Other</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -773,7 +773,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>inspector_info</t>
+          <t>inspector_info_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Other (specify)</t>
+          <t>Inspector Info Comments Other</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Other (description)</t>
+          <t>Inspector Info Comments Other Description</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Other (specify)</t>
+          <t>Inspection Type Other</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Other (description)</t>
+          <t>Inspection Type Other Description</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Other (specify)</t>
+          <t>Inspection Notes Other</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Other (description)</t>
+          <t>Inspection Notes Other Description</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>inspector_info_organisation A</t>
+          <t>inspector info organisation A</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>inspector_info_organisation B</t>
+          <t>inspector info organisation B</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>inspector_info_organisation C</t>
+          <t>inspector info organisation C</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>inspector_info_function A</t>
+          <t>inspector info function A</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>inspector_info_function B</t>
+          <t>inspector info function B</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>inspector_info_function C</t>
+          <t>inspector info function C</t>
         </is>
       </c>
     </row>
